--- a/output/variance_report.xlsx
+++ b/output/variance_report.xlsx
@@ -9,9 +9,12 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Material Misses" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="By Department" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="By Month" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variance Data" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Near Misses" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="By Department" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="By Month" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Quality" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Integrity Checks" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variance Data" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,10 +23,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="$#,##0;($#,##0)"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="0.0%;(0.0%)"/>
+    <numFmt numFmtId="167" formatCode="0.0&quot;x&quot;"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -54,11 +58,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -424,10 +429,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -486,7 +491,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Gross misses</t>
+          <t>Gross misses (all misses combined)</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
@@ -496,61 +501,91 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Gross accuracy</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>0.9572618845267281</v>
+          <t>Misses that cancelled out</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>1156098</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Material misses (of 96)</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>7</v>
+          <t>Gross accuracy</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>0.9572618845267281</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Jan-Aug variance</t>
-        </is>
-      </c>
-      <c r="B9" s="1" t="n">
-        <v>247760</v>
+          <t>Material misses (of 96)</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sep-Dec variance</t>
-        </is>
-      </c>
-      <c r="B10" s="1" t="n">
-        <v>-297805</v>
+          <t>Near misses (of 96)</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Materiality: % threshold</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>0.05</v>
+          <t>Jan-Aug variance</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>247760</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Sep-Dec variance</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>-297805</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Materiality: % threshold</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>Materiality: $ threshold</t>
         </is>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B14" s="1" t="n">
         <v>25000</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Near miss: % floor</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>0.04</v>
       </c>
     </row>
   </sheetData>
@@ -827,7 +862,183 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>department</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>month_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>budget</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>variance</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>variance_pct</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>fav_unfav</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="n">
+        <v>1239326</v>
+      </c>
+      <c r="D2" s="1" t="n">
+        <v>1178634</v>
+      </c>
+      <c r="E2" s="1" t="n">
+        <v>-60692</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>-0.04897177982225823</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Favorable</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Apr</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="n">
+        <v>831785</v>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>870830</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>39045</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>0.04694121678077869</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Unfavorable</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Customer Success</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Dec</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>697211</v>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>664526</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>-32685</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>-0.04687963901889098</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Favorable</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>913634</v>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>955629</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>41995</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>0.04596479553081431</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Unfavorable</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -836,9 +1047,12 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -874,17 +1088,32 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>min_month_budget</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>max_month_budget</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>variance_pct</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>gross_accuracy</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>fav_unfav</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>phasing_ratio</t>
         </is>
       </c>
     </row>
@@ -909,16 +1138,25 @@
       <c r="F2" t="n">
         <v>1</v>
       </c>
-      <c r="G2" s="3" t="n">
+      <c r="G2" s="1" t="n">
+        <v>4280</v>
+      </c>
+      <c r="H2" s="1" t="n">
+        <v>1310207</v>
+      </c>
+      <c r="I2" s="3" t="n">
         <v>0.02089994670534936</v>
       </c>
-      <c r="H2" s="3" t="n">
+      <c r="J2" s="3" t="n">
         <v>0.9580502079724718</v>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>Unfavorable</t>
         </is>
+      </c>
+      <c r="L2" s="4" t="n">
+        <v>306.1231308411215</v>
       </c>
     </row>
     <row r="3">
@@ -942,16 +1180,25 @@
       <c r="F3" t="n">
         <v>0</v>
       </c>
-      <c r="G3" s="3" t="n">
+      <c r="G3" s="1" t="n">
+        <v>28305</v>
+      </c>
+      <c r="H3" s="1" t="n">
+        <v>592649</v>
+      </c>
+      <c r="I3" s="3" t="n">
         <v>0.02742272062929682</v>
       </c>
-      <c r="H3" s="3" t="n">
+      <c r="J3" s="3" t="n">
         <v>0.9547393649852107</v>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>Unfavorable</t>
         </is>
+      </c>
+      <c r="L3" s="4" t="n">
+        <v>20.93796149090267</v>
       </c>
     </row>
     <row r="4">
@@ -975,16 +1222,25 @@
       <c r="F4" t="n">
         <v>1</v>
       </c>
-      <c r="G4" s="3" t="n">
+      <c r="G4" s="1" t="n">
+        <v>37393</v>
+      </c>
+      <c r="H4" s="1" t="n">
+        <v>1239326</v>
+      </c>
+      <c r="I4" s="3" t="n">
         <v>0.005775457079803877</v>
       </c>
-      <c r="H4" s="3" t="n">
+      <c r="J4" s="3" t="n">
         <v>0.9589632552353831</v>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>Unfavorable</t>
         </is>
+      </c>
+      <c r="L4" s="4" t="n">
+        <v>33.14326210788116</v>
       </c>
     </row>
     <row r="5">
@@ -1008,16 +1264,25 @@
       <c r="F5" t="n">
         <v>1</v>
       </c>
-      <c r="G5" s="3" t="n">
+      <c r="G5" s="1" t="n">
+        <v>22781</v>
+      </c>
+      <c r="H5" s="1" t="n">
+        <v>1107759</v>
+      </c>
+      <c r="I5" s="3" t="n">
         <v>0.007722811684106601</v>
       </c>
-      <c r="H5" s="3" t="n">
+      <c r="J5" s="3" t="n">
         <v>0.9578074258811463</v>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>Unfavorable</t>
         </is>
+      </c>
+      <c r="L5" s="4" t="n">
+        <v>48.62644308853869</v>
       </c>
     </row>
     <row r="6">
@@ -1041,16 +1306,25 @@
       <c r="F6" t="n">
         <v>1</v>
       </c>
-      <c r="G6" s="3" t="n">
+      <c r="G6" s="1" t="n">
+        <v>15447</v>
+      </c>
+      <c r="H6" s="1" t="n">
+        <v>936211</v>
+      </c>
+      <c r="I6" s="3" t="n">
         <v>0.003051640043079107</v>
       </c>
-      <c r="H6" s="3" t="n">
+      <c r="J6" s="3" t="n">
         <v>0.9575853745699102</v>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>Unfavorable</t>
         </is>
+      </c>
+      <c r="L6" s="4" t="n">
+        <v>60.60794976370816</v>
       </c>
     </row>
     <row r="7">
@@ -1074,16 +1348,25 @@
       <c r="F7" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="3" t="n">
+      <c r="G7" s="1" t="n">
+        <v>1363</v>
+      </c>
+      <c r="H7" s="1" t="n">
+        <v>697211</v>
+      </c>
+      <c r="I7" s="3" t="n">
         <v>-0.02348946061406735</v>
       </c>
-      <c r="H7" s="3" t="n">
+      <c r="J7" s="3" t="n">
         <v>0.9604637965396856</v>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>Favorable</t>
         </is>
+      </c>
+      <c r="L7" s="4" t="n">
+        <v>511.5267791636097</v>
       </c>
     </row>
     <row r="8">
@@ -1107,16 +1390,25 @@
       <c r="F8" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="3" t="n">
+      <c r="G8" s="1" t="n">
+        <v>6473</v>
+      </c>
+      <c r="H8" s="1" t="n">
+        <v>1090283</v>
+      </c>
+      <c r="I8" s="3" t="n">
         <v>-0.02608294572001024</v>
       </c>
-      <c r="H8" s="3" t="n">
+      <c r="J8" s="3" t="n">
         <v>0.9683025542682512</v>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>Favorable</t>
         </is>
+      </c>
+      <c r="L8" s="4" t="n">
+        <v>168.4355013131469</v>
       </c>
     </row>
     <row r="9">
@@ -1140,16 +1432,25 @@
       <c r="F9" t="n">
         <v>3</v>
       </c>
-      <c r="G9" s="3" t="n">
+      <c r="G9" s="1" t="n">
+        <v>27468</v>
+      </c>
+      <c r="H9" s="1" t="n">
+        <v>912818</v>
+      </c>
+      <c r="I9" s="3" t="n">
         <v>-0.02925429540344451</v>
       </c>
-      <c r="H9" s="3" t="n">
+      <c r="J9" s="3" t="n">
         <v>0.9429387907726675</v>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>Favorable</t>
         </is>
+      </c>
+      <c r="L9" s="4" t="n">
+        <v>33.23205184214358</v>
       </c>
     </row>
   </sheetData>
@@ -1157,7 +1458,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1559,13 +1860,367 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I97"/>
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>department</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>min_month_budget</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>max_month_budget</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>phasing_ratio</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>flag</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Customer Success</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>1363</v>
+      </c>
+      <c r="C2" s="1" t="n">
+        <v>697211</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>511.5267791636097</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Question this phasing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>4280</v>
+      </c>
+      <c r="C3" s="1" t="n">
+        <v>1310207</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>306.1231308411215</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Question this phasing</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>6473</v>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>1090283</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>168.4355013131469</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Question this phasing</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>15447</v>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>936211</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>60.60794976370816</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Question this phasing</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>22781</v>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>1107759</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>48.62644308853869</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Question this phasing</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>27468</v>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>912818</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>33.23205184214358</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Question this phasing</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>37393</v>
+      </c>
+      <c r="C8" s="1" t="n">
+        <v>1239326</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>33.14326210788116</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Question this phasing</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>28305</v>
+      </c>
+      <c r="C9" s="1" t="n">
+        <v>592649</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>20.93796149090267</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Question this phasing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>One row per department-month</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Budget in = budget out</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Actual in = actual out</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Department totals add to the grand total</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Monthly totals add to the annual total</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Year-to-date variance ends at the net variance</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Variance = actual - budget on every row</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Gross misses &gt;= |net variance|</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Material and near-miss flags never overlap</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1577,6 +2232,7 @@
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1625,11 +2281,16 @@
           <t>material_miss</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>near_miss</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Customer Success</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1638,33 +2299,36 @@
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>284101</v>
+        <v>1363</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>267910</v>
+        <v>1476</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>-16191</v>
+        <v>113</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>-0.05699029570469657</v>
+        <v>0.08290535583272193</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Favorable</t>
+          <t>Unfavorable</t>
         </is>
       </c>
       <c r="H2" s="1" t="n">
-        <v>16191</v>
+        <v>113</v>
       </c>
       <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Customer Success</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1673,16 +2337,16 @@
         </is>
       </c>
       <c r="C3" s="1" t="n">
-        <v>52786</v>
+        <v>139699</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>50926</v>
+        <v>133457</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>-1860</v>
+        <v>-6242</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>-0.03523661576933278</v>
+        <v>-0.04468178011295714</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -1690,16 +2354,19 @@
         </is>
       </c>
       <c r="H3" s="1" t="n">
-        <v>1860</v>
+        <v>6242</v>
       </c>
       <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Customer Success</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1708,33 +2375,36 @@
         </is>
       </c>
       <c r="C4" s="1" t="n">
-        <v>52777</v>
+        <v>105579</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>53012</v>
+        <v>105526</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>235</v>
+        <v>-53</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.004452697197642913</v>
+        <v>-0.0005019937677000161</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Unfavorable</t>
+          <t>Favorable</t>
         </is>
       </c>
       <c r="H4" s="1" t="n">
-        <v>235</v>
+        <v>53</v>
       </c>
       <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Customer Success</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1743,16 +2413,16 @@
         </is>
       </c>
       <c r="C5" s="1" t="n">
-        <v>18621</v>
+        <v>49083</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>18392</v>
+        <v>47323</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>-229</v>
+        <v>-1760</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>-0.01229794318242844</v>
+        <v>-0.03585762891428804</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1760,16 +2430,19 @@
         </is>
       </c>
       <c r="H5" s="1" t="n">
-        <v>229</v>
+        <v>1760</v>
       </c>
       <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Customer Success</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1778,16 +2451,16 @@
         </is>
       </c>
       <c r="C6" s="1" t="n">
-        <v>625881</v>
+        <v>24951</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>602361</v>
+        <v>23984</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>-23520</v>
+        <v>-967</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>-0.03757902860128363</v>
+        <v>-0.03875596168490241</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1795,16 +2468,19 @@
         </is>
       </c>
       <c r="H6" s="1" t="n">
-        <v>23520</v>
+        <v>967</v>
       </c>
       <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Customer Success</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1813,33 +2489,36 @@
         </is>
       </c>
       <c r="C7" s="1" t="n">
-        <v>286012</v>
+        <v>80494</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>291770</v>
+        <v>73783</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>5758</v>
+        <v>-6711</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.02013202243262521</v>
+        <v>-0.08337267373965761</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Unfavorable</t>
+          <t>Favorable</t>
         </is>
       </c>
       <c r="H7" s="1" t="n">
-        <v>5758</v>
+        <v>6711</v>
       </c>
       <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Customer Success</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1848,33 +2527,36 @@
         </is>
       </c>
       <c r="C8" s="1" t="n">
-        <v>383156</v>
+        <v>559505</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>358292</v>
+        <v>570539</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>-24864</v>
+        <v>11034</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>-0.06489262858992161</v>
+        <v>0.01972100338692237</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Favorable</t>
+          <t>Unfavorable</t>
         </is>
       </c>
       <c r="H8" s="1" t="n">
-        <v>24864</v>
+        <v>11034</v>
       </c>
       <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Customer Success</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1883,33 +2565,36 @@
         </is>
       </c>
       <c r="C9" s="1" t="n">
-        <v>6473</v>
+        <v>76288</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>6230</v>
+        <v>76324</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>-243</v>
+        <v>36</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>-0.03754055306658427</v>
+        <v>0.0004718959731543624</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Favorable</t>
+          <t>Unfavorable</t>
         </is>
       </c>
       <c r="H9" s="1" t="n">
-        <v>243</v>
+        <v>36</v>
       </c>
       <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Customer Success</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1918,16 +2603,16 @@
         </is>
       </c>
       <c r="C10" s="1" t="n">
-        <v>1090283</v>
+        <v>142939</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>1064056</v>
+        <v>131398</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>-26227</v>
+        <v>-11541</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>-0.02405522235969927</v>
+        <v>-0.08074073555852497</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1935,16 +2620,19 @@
         </is>
       </c>
       <c r="H10" s="1" t="n">
-        <v>26227</v>
+        <v>11541</v>
       </c>
       <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Customer Success</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1953,16 +2641,16 @@
         </is>
       </c>
       <c r="C11" s="1" t="n">
-        <v>555924</v>
+        <v>237254</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>551528</v>
+        <v>227800</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>-4396</v>
+        <v>-9454</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.007907555709053755</v>
+        <v>-0.03984758950323282</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1970,16 +2658,19 @@
         </is>
       </c>
       <c r="H11" s="1" t="n">
-        <v>4396</v>
+        <v>9454</v>
       </c>
       <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Customer Success</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1988,16 +2679,16 @@
         </is>
       </c>
       <c r="C12" s="1" t="n">
-        <v>74278</v>
+        <v>88324</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>78090</v>
+        <v>94814</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>3812</v>
+        <v>6490</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.05132071407415385</v>
+        <v>0.07347946198088855</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -2005,16 +2696,19 @@
         </is>
       </c>
       <c r="H12" s="1" t="n">
-        <v>3812</v>
+        <v>6490</v>
       </c>
       <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Customer Success</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2023,16 +2717,16 @@
         </is>
       </c>
       <c r="C13" s="1" t="n">
-        <v>62450</v>
+        <v>697211</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>59074</v>
+        <v>664526</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>-3376</v>
+        <v>-32685</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>-0.05405924739791833</v>
+        <v>-0.04687963901889098</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -2040,16 +2734,19 @@
         </is>
       </c>
       <c r="H13" s="1" t="n">
-        <v>3376</v>
+        <v>32685</v>
       </c>
       <c r="I13" t="b">
         <v>0</v>
+      </c>
+      <c r="J13" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2058,16 +2755,16 @@
         </is>
       </c>
       <c r="C14" s="1" t="n">
-        <v>1310207</v>
+        <v>204546</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>1353427</v>
+        <v>215530</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>43220</v>
+        <v>10984</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.03298715393827082</v>
+        <v>0.0536994123571226</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -2075,16 +2772,19 @@
         </is>
       </c>
       <c r="H14" s="1" t="n">
-        <v>43220</v>
+        <v>10984</v>
       </c>
       <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2093,33 +2793,36 @@
         </is>
       </c>
       <c r="C15" s="1" t="n">
-        <v>201517</v>
+        <v>160450</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>205506</v>
+        <v>150362</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>3989</v>
+        <v>-10088</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.01979485601711022</v>
+        <v>-0.0628731692115924</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Unfavorable</t>
+          <t>Favorable</t>
         </is>
       </c>
       <c r="H15" s="1" t="n">
-        <v>3989</v>
+        <v>10088</v>
       </c>
       <c r="I15" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2128,16 +2831,16 @@
         </is>
       </c>
       <c r="C16" s="1" t="n">
-        <v>629971</v>
+        <v>217501</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>667753</v>
+        <v>217821</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>37782</v>
+        <v>320</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.05997418928807834</v>
+        <v>0.001471257603413318</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -2145,16 +2848,19 @@
         </is>
       </c>
       <c r="H16" s="1" t="n">
-        <v>37782</v>
+        <v>320</v>
       </c>
       <c r="I16" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="J16" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2163,33 +2869,36 @@
         </is>
       </c>
       <c r="C17" s="1" t="n">
-        <v>365478</v>
+        <v>242694</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>343989</v>
+        <v>251248</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>-21489</v>
+        <v>8554</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-0.05879697273160081</v>
+        <v>0.0352460299801396</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Favorable</t>
+          <t>Unfavorable</t>
         </is>
       </c>
       <c r="H17" s="1" t="n">
-        <v>21489</v>
+        <v>8554</v>
       </c>
       <c r="I17" t="b">
+        <v>0</v>
+      </c>
+      <c r="J17" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2198,33 +2907,36 @@
         </is>
       </c>
       <c r="C18" s="1" t="n">
-        <v>191888</v>
+        <v>22781</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>188125</v>
+        <v>24250</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>-3763</v>
+        <v>1469</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>-0.01961039773201034</v>
+        <v>0.06448356086212194</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Favorable</t>
+          <t>Unfavorable</t>
         </is>
       </c>
       <c r="H18" s="1" t="n">
-        <v>3763</v>
+        <v>1469</v>
       </c>
       <c r="I18" t="b">
+        <v>0</v>
+      </c>
+      <c r="J18" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2233,16 +2945,16 @@
         </is>
       </c>
       <c r="C19" s="1" t="n">
-        <v>4280</v>
+        <v>124695</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>4035</v>
+        <v>120788</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>-245</v>
+        <v>-3907</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>-0.05724299065420561</v>
+        <v>-0.03133245118088135</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -2250,16 +2962,19 @@
         </is>
       </c>
       <c r="H19" s="1" t="n">
-        <v>245</v>
+        <v>3907</v>
       </c>
       <c r="I19" t="b">
+        <v>0</v>
+      </c>
+      <c r="J19" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2268,33 +2983,36 @@
         </is>
       </c>
       <c r="C20" s="1" t="n">
-        <v>913634</v>
+        <v>74922</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>955629</v>
+        <v>71149</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>41995</v>
+        <v>-3773</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.04596479553081431</v>
+        <v>-0.05035904006833774</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Unfavorable</t>
+          <t>Favorable</t>
         </is>
       </c>
       <c r="H20" s="1" t="n">
-        <v>41995</v>
+        <v>3773</v>
       </c>
       <c r="I20" t="b">
+        <v>0</v>
+      </c>
+      <c r="J20" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2303,33 +3021,36 @@
         </is>
       </c>
       <c r="C21" s="1" t="n">
-        <v>265515</v>
+        <v>439148</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>261937</v>
+        <v>455838</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>-3578</v>
+        <v>16690</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>-0.01347569817147807</v>
+        <v>0.03800541047665024</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Favorable</t>
+          <t>Unfavorable</t>
         </is>
       </c>
       <c r="H21" s="1" t="n">
-        <v>3578</v>
+        <v>16690</v>
       </c>
       <c r="I21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J21" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2338,33 +3059,36 @@
         </is>
       </c>
       <c r="C22" s="1" t="n">
-        <v>156015</v>
+        <v>171698</v>
       </c>
       <c r="D22" s="1" t="n">
-        <v>147813</v>
+        <v>181263</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>-8202</v>
+        <v>9565</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>-0.05257186808960677</v>
+        <v>0.05570827848897483</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Favorable</t>
+          <t>Unfavorable</t>
         </is>
       </c>
       <c r="H22" s="1" t="n">
-        <v>8202</v>
+        <v>9565</v>
       </c>
       <c r="I22" t="b">
+        <v>0</v>
+      </c>
+      <c r="J22" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2373,33 +3097,36 @@
         </is>
       </c>
       <c r="C23" s="1" t="n">
-        <v>5158</v>
+        <v>1107759</v>
       </c>
       <c r="D23" s="1" t="n">
-        <v>5220</v>
+        <v>1077583</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>62</v>
+        <v>-30176</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.01202016285381931</v>
+        <v>-0.02724058211217422</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Unfavorable</t>
+          <t>Favorable</t>
         </is>
       </c>
       <c r="H23" s="1" t="n">
-        <v>62</v>
+        <v>30176</v>
       </c>
       <c r="I23" t="b">
+        <v>0</v>
+      </c>
+      <c r="J23" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2408,16 +3135,16 @@
         </is>
       </c>
       <c r="C24" s="1" t="n">
-        <v>84135</v>
+        <v>137497</v>
       </c>
       <c r="D24" s="1" t="n">
-        <v>77037</v>
+        <v>127502</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>-7098</v>
+        <v>-9995</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>-0.08436441433410589</v>
+        <v>-0.07269249510898419</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -2425,16 +3152,19 @@
         </is>
       </c>
       <c r="H24" s="1" t="n">
-        <v>7098</v>
+        <v>9995</v>
       </c>
       <c r="I24" t="b">
+        <v>0</v>
+      </c>
+      <c r="J24" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2443,16 +3173,16 @@
         </is>
       </c>
       <c r="C25" s="1" t="n">
-        <v>88385</v>
+        <v>458038</v>
       </c>
       <c r="D25" s="1" t="n">
-        <v>93830</v>
+        <v>494357</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>5445</v>
+        <v>36319</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>0.06160547604231487</v>
+        <v>0.07929254777987853</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -2460,16 +3190,19 @@
         </is>
       </c>
       <c r="H25" s="1" t="n">
-        <v>5445</v>
+        <v>36319</v>
       </c>
       <c r="I25" t="b">
+        <v>1</v>
+      </c>
+      <c r="J25" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2478,33 +3211,36 @@
         </is>
       </c>
       <c r="C26" s="1" t="n">
-        <v>936211</v>
+        <v>176168</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>899294</v>
+        <v>180398</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>-36917</v>
+        <v>4230</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>-0.03943235018601576</v>
+        <v>0.02401117115480678</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Favorable</t>
+          <t>Unfavorable</t>
         </is>
       </c>
       <c r="H26" s="1" t="n">
-        <v>36917</v>
+        <v>4230</v>
       </c>
       <c r="I26" t="b">
+        <v>0</v>
+      </c>
+      <c r="J26" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2513,16 +3249,16 @@
         </is>
       </c>
       <c r="C27" s="1" t="n">
-        <v>751664</v>
+        <v>331631</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>757440</v>
+        <v>353804</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>5776</v>
+        <v>22173</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.007684284467528044</v>
+        <v>0.06686045635058242</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -2530,16 +3266,19 @@
         </is>
       </c>
       <c r="H27" s="1" t="n">
-        <v>5776</v>
+        <v>22173</v>
       </c>
       <c r="I27" t="b">
+        <v>0</v>
+      </c>
+      <c r="J27" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2548,33 +3287,36 @@
         </is>
       </c>
       <c r="C28" s="1" t="n">
-        <v>304068</v>
+        <v>1111570</v>
       </c>
       <c r="D28" s="1" t="n">
-        <v>284414</v>
+        <v>1172329</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>-19654</v>
+        <v>60759</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>-0.06463685754502282</v>
+        <v>0.05466052520309112</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Favorable</t>
+          <t>Unfavorable</t>
         </is>
       </c>
       <c r="H28" s="1" t="n">
-        <v>19654</v>
+        <v>60759</v>
       </c>
       <c r="I28" t="b">
+        <v>1</v>
+      </c>
+      <c r="J28" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2583,33 +3325,36 @@
         </is>
       </c>
       <c r="C29" s="1" t="n">
-        <v>850883</v>
+        <v>133849</v>
       </c>
       <c r="D29" s="1" t="n">
-        <v>897167</v>
+        <v>126297</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>-7552</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.05439525763236544</v>
+        <v>-0.05642178873207868</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Unfavorable</t>
+          <t>Favorable</t>
         </is>
       </c>
       <c r="H29" s="1" t="n">
-        <v>46284</v>
+        <v>7552</v>
       </c>
       <c r="I29" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="J29" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2618,33 +3363,36 @@
         </is>
       </c>
       <c r="C30" s="1" t="n">
-        <v>30924</v>
+        <v>246601</v>
       </c>
       <c r="D30" s="1" t="n">
-        <v>28555</v>
+        <v>264025</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>-2369</v>
+        <v>17424</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-0.07660716595524512</v>
+        <v>0.07065664778326122</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Favorable</t>
+          <t>Unfavorable</t>
         </is>
       </c>
       <c r="H30" s="1" t="n">
-        <v>2369</v>
+        <v>17424</v>
       </c>
       <c r="I30" t="b">
+        <v>0</v>
+      </c>
+      <c r="J30" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2653,16 +3401,16 @@
         </is>
       </c>
       <c r="C31" s="1" t="n">
-        <v>72803</v>
+        <v>657601</v>
       </c>
       <c r="D31" s="1" t="n">
-        <v>79183</v>
+        <v>662257</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>6380</v>
+        <v>4656</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0.08763375135640016</v>
+        <v>0.00708028120395194</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -2670,16 +3418,19 @@
         </is>
       </c>
       <c r="H31" s="1" t="n">
-        <v>6380</v>
+        <v>4656</v>
       </c>
       <c r="I31" t="b">
+        <v>0</v>
+      </c>
+      <c r="J31" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2688,16 +3439,16 @@
         </is>
       </c>
       <c r="C32" s="1" t="n">
-        <v>15447</v>
+        <v>121277</v>
       </c>
       <c r="D32" s="1" t="n">
-        <v>16203</v>
+        <v>127988</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>756</v>
+        <v>6711</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>0.04894154204699942</v>
+        <v>0.05533613133570257</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -2705,16 +3456,19 @@
         </is>
       </c>
       <c r="H32" s="1" t="n">
-        <v>756</v>
+        <v>6711</v>
       </c>
       <c r="I32" t="b">
+        <v>0</v>
+      </c>
+      <c r="J32" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2723,33 +3477,36 @@
         </is>
       </c>
       <c r="C33" s="1" t="n">
-        <v>131343</v>
+        <v>37393</v>
       </c>
       <c r="D33" s="1" t="n">
-        <v>124220</v>
+        <v>40058</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>-7123</v>
+        <v>2665</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>-0.0542320489101056</v>
+        <v>0.07127002380124622</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Favorable</t>
+          <t>Unfavorable</t>
         </is>
       </c>
       <c r="H33" s="1" t="n">
-        <v>7123</v>
+        <v>2665</v>
       </c>
       <c r="I33" t="b">
+        <v>0</v>
+      </c>
+      <c r="J33" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2758,16 +3515,16 @@
         </is>
       </c>
       <c r="C34" s="1" t="n">
-        <v>164250</v>
+        <v>159710</v>
       </c>
       <c r="D34" s="1" t="n">
-        <v>149630</v>
+        <v>154478</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>-14620</v>
+        <v>-5232</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>-0.08901065449010655</v>
+        <v>-0.03275937636967002</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -2775,16 +3532,19 @@
         </is>
       </c>
       <c r="H34" s="1" t="n">
-        <v>14620</v>
+        <v>5232</v>
       </c>
       <c r="I34" t="b">
+        <v>0</v>
+      </c>
+      <c r="J34" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2793,33 +3553,36 @@
         </is>
       </c>
       <c r="C35" s="1" t="n">
-        <v>105653</v>
+        <v>82067</v>
       </c>
       <c r="D35" s="1" t="n">
-        <v>111652</v>
+        <v>76306</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>5999</v>
+        <v>-5761</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>0.05678021447568928</v>
+        <v>-0.07019874005385843</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Unfavorable</t>
+          <t>Favorable</t>
         </is>
       </c>
       <c r="H35" s="1" t="n">
-        <v>5999</v>
+        <v>5761</v>
       </c>
       <c r="I35" t="b">
+        <v>0</v>
+      </c>
+      <c r="J35" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2828,33 +3591,36 @@
         </is>
       </c>
       <c r="C36" s="1" t="n">
-        <v>588928</v>
+        <v>1239326</v>
       </c>
       <c r="D36" s="1" t="n">
-        <v>610856</v>
+        <v>1178634</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>21928</v>
+        <v>-60692</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.03723375353184091</v>
+        <v>-0.04897177982225823</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Unfavorable</t>
+          <t>Favorable</t>
         </is>
       </c>
       <c r="H36" s="1" t="n">
-        <v>21928</v>
+        <v>60692</v>
       </c>
       <c r="I36" t="b">
         <v>0</v>
+      </c>
+      <c r="J36" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2863,33 +3629,36 @@
         </is>
       </c>
       <c r="C37" s="1" t="n">
-        <v>147261</v>
+        <v>770631</v>
       </c>
       <c r="D37" s="1" t="n">
-        <v>153331</v>
+        <v>760519</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>6070</v>
+        <v>-10112</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>0.04121933166282994</v>
+        <v>-0.01312171454301735</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Unfavorable</t>
+          <t>Favorable</t>
         </is>
       </c>
       <c r="H37" s="1" t="n">
-        <v>6070</v>
+        <v>10112</v>
       </c>
       <c r="I37" t="b">
+        <v>0</v>
+      </c>
+      <c r="J37" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>R&amp;D</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2898,33 +3667,36 @@
         </is>
       </c>
       <c r="C38" s="1" t="n">
-        <v>32179</v>
+        <v>107335</v>
       </c>
       <c r="D38" s="1" t="n">
-        <v>32018</v>
+        <v>116922</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>-161</v>
+        <v>9587</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>-0.005003262997607135</v>
+        <v>0.08931848884334094</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Favorable</t>
+          <t>Unfavorable</t>
         </is>
       </c>
       <c r="H38" s="1" t="n">
-        <v>161</v>
+        <v>9587</v>
       </c>
       <c r="I38" t="b">
+        <v>0</v>
+      </c>
+      <c r="J38" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>R&amp;D</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2933,33 +3705,36 @@
         </is>
       </c>
       <c r="C39" s="1" t="n">
-        <v>185677</v>
+        <v>267622</v>
       </c>
       <c r="D39" s="1" t="n">
-        <v>172963</v>
+        <v>290042</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>-12714</v>
+        <v>22420</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>-0.06847374742159772</v>
+        <v>0.08377487650492112</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Favorable</t>
+          <t>Unfavorable</t>
         </is>
       </c>
       <c r="H39" s="1" t="n">
-        <v>12714</v>
+        <v>22420</v>
       </c>
       <c r="I39" t="b">
+        <v>0</v>
+      </c>
+      <c r="J39" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>R&amp;D</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2968,16 +3743,16 @@
         </is>
       </c>
       <c r="C40" s="1" t="n">
-        <v>51513</v>
+        <v>165729</v>
       </c>
       <c r="D40" s="1" t="n">
-        <v>53490</v>
+        <v>167467</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>1977</v>
+        <v>1738</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0.03837866169704734</v>
+        <v>0.01048699986121922</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2985,16 +3760,19 @@
         </is>
       </c>
       <c r="H40" s="1" t="n">
-        <v>1977</v>
+        <v>1738</v>
       </c>
       <c r="I40" t="b">
+        <v>0</v>
+      </c>
+      <c r="J40" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>R&amp;D</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3003,16 +3781,16 @@
         </is>
       </c>
       <c r="C41" s="1" t="n">
-        <v>831785</v>
+        <v>195575</v>
       </c>
       <c r="D41" s="1" t="n">
-        <v>870830</v>
+        <v>209045</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>39045</v>
+        <v>13470</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0.04694121678077869</v>
+        <v>0.06887383356768503</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -3020,16 +3798,19 @@
         </is>
       </c>
       <c r="H41" s="1" t="n">
-        <v>39045</v>
+        <v>13470</v>
       </c>
       <c r="I41" t="b">
+        <v>0</v>
+      </c>
+      <c r="J41" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>R&amp;D</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3038,33 +3819,36 @@
         </is>
       </c>
       <c r="C42" s="1" t="n">
-        <v>408379</v>
+        <v>34520</v>
       </c>
       <c r="D42" s="1" t="n">
-        <v>412883</v>
+        <v>32585</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>4504</v>
+        <v>-1935</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>0.01102897063756951</v>
+        <v>-0.05605446118192352</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Unfavorable</t>
+          <t>Favorable</t>
         </is>
       </c>
       <c r="H42" s="1" t="n">
-        <v>4504</v>
+        <v>1935</v>
       </c>
       <c r="I42" t="b">
+        <v>0</v>
+      </c>
+      <c r="J42" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>R&amp;D</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3073,33 +3857,36 @@
         </is>
       </c>
       <c r="C43" s="1" t="n">
-        <v>168077</v>
+        <v>114751</v>
       </c>
       <c r="D43" s="1" t="n">
-        <v>176274</v>
+        <v>110183</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>8197</v>
+        <v>-4568</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>0.04876931406438716</v>
+        <v>-0.03980793195701998</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Unfavorable</t>
+          <t>Favorable</t>
         </is>
       </c>
       <c r="H43" s="1" t="n">
-        <v>8197</v>
+        <v>4568</v>
       </c>
       <c r="I43" t="b">
+        <v>0</v>
+      </c>
+      <c r="J43" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>R&amp;D</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3108,33 +3895,36 @@
         </is>
       </c>
       <c r="C44" s="1" t="n">
-        <v>27468</v>
+        <v>175143</v>
       </c>
       <c r="D44" s="1" t="n">
-        <v>27437</v>
+        <v>181459</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>-31</v>
+        <v>6316</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>-0.001128585990971312</v>
+        <v>0.03606196079774813</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Favorable</t>
+          <t>Unfavorable</t>
         </is>
       </c>
       <c r="H44" s="1" t="n">
-        <v>31</v>
+        <v>6316</v>
       </c>
       <c r="I44" t="b">
+        <v>0</v>
+      </c>
+      <c r="J44" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>R&amp;D</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3143,16 +3933,16 @@
         </is>
       </c>
       <c r="C45" s="1" t="n">
-        <v>155809</v>
+        <v>38190</v>
       </c>
       <c r="D45" s="1" t="n">
-        <v>156446</v>
+        <v>40573</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>637</v>
+        <v>2383</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>0.004088338927789794</v>
+        <v>0.06239853364755171</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -3160,16 +3950,19 @@
         </is>
       </c>
       <c r="H45" s="1" t="n">
-        <v>637</v>
+        <v>2383</v>
       </c>
       <c r="I45" t="b">
+        <v>0</v>
+      </c>
+      <c r="J45" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>R&amp;D</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3178,33 +3971,36 @@
         </is>
       </c>
       <c r="C46" s="1" t="n">
-        <v>164520</v>
+        <v>28305</v>
       </c>
       <c r="D46" s="1" t="n">
-        <v>162374</v>
+        <v>30120</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>-2146</v>
+        <v>1815</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>-0.01304400680768296</v>
+        <v>0.06412294647588765</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Favorable</t>
+          <t>Unfavorable</t>
         </is>
       </c>
       <c r="H46" s="1" t="n">
-        <v>2146</v>
+        <v>1815</v>
       </c>
       <c r="I46" t="b">
+        <v>0</v>
+      </c>
+      <c r="J46" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>R&amp;D</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3213,16 +4009,16 @@
         </is>
       </c>
       <c r="C47" s="1" t="n">
-        <v>547074</v>
+        <v>592649</v>
       </c>
       <c r="D47" s="1" t="n">
-        <v>500340</v>
+        <v>582462</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>-46734</v>
+        <v>-10187</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>-0.08542537207032321</v>
+        <v>-0.01718892632907505</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -3230,16 +4026,19 @@
         </is>
       </c>
       <c r="H47" s="1" t="n">
-        <v>46734</v>
+        <v>10187</v>
       </c>
       <c r="I47" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="J47" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>R&amp;D</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3248,33 +4047,36 @@
         </is>
       </c>
       <c r="C48" s="1" t="n">
-        <v>424520</v>
+        <v>106995</v>
       </c>
       <c r="D48" s="1" t="n">
-        <v>394557</v>
+        <v>114463</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>-29963</v>
+        <v>7468</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>-0.07058089135965326</v>
+        <v>0.06979765409598579</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Favorable</t>
+          <t>Unfavorable</t>
         </is>
       </c>
       <c r="H48" s="1" t="n">
-        <v>29963</v>
+        <v>7468</v>
       </c>
       <c r="I48" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="J48" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>R&amp;D</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3283,33 +4085,36 @@
         </is>
       </c>
       <c r="C49" s="1" t="n">
-        <v>912818</v>
+        <v>44481</v>
       </c>
       <c r="D49" s="1" t="n">
-        <v>835828</v>
+        <v>47290</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>-76990</v>
+        <v>2809</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>-0.08434320970883571</v>
+        <v>0.06315055866549762</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Favorable</t>
+          <t>Unfavorable</t>
         </is>
       </c>
       <c r="H49" s="1" t="n">
-        <v>76990</v>
+        <v>2809</v>
       </c>
       <c r="I49" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="J49" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3318,16 +4123,16 @@
         </is>
       </c>
       <c r="C50" s="1" t="n">
-        <v>176168</v>
+        <v>1310207</v>
       </c>
       <c r="D50" s="1" t="n">
-        <v>180398</v>
+        <v>1353427</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>4230</v>
+        <v>43220</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>0.02401117115480678</v>
+        <v>0.03298715393827082</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -3335,16 +4140,19 @@
         </is>
       </c>
       <c r="H50" s="1" t="n">
-        <v>4230</v>
+        <v>43220</v>
       </c>
       <c r="I50" t="b">
+        <v>0</v>
+      </c>
+      <c r="J50" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3353,16 +4161,16 @@
         </is>
       </c>
       <c r="C51" s="1" t="n">
-        <v>331631</v>
+        <v>201517</v>
       </c>
       <c r="D51" s="1" t="n">
-        <v>353804</v>
+        <v>205506</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>22173</v>
+        <v>3989</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>0.06686045635058242</v>
+        <v>0.01979485601711022</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -3370,16 +4178,19 @@
         </is>
       </c>
       <c r="H51" s="1" t="n">
-        <v>22173</v>
+        <v>3989</v>
       </c>
       <c r="I51" t="b">
+        <v>0</v>
+      </c>
+      <c r="J51" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3388,16 +4199,16 @@
         </is>
       </c>
       <c r="C52" s="1" t="n">
-        <v>1111570</v>
+        <v>629971</v>
       </c>
       <c r="D52" s="1" t="n">
-        <v>1172329</v>
+        <v>667753</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>60759</v>
+        <v>37782</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>0.05466052520309112</v>
+        <v>0.05997418928807834</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -3405,16 +4216,19 @@
         </is>
       </c>
       <c r="H52" s="1" t="n">
-        <v>60759</v>
+        <v>37782</v>
       </c>
       <c r="I52" t="b">
         <v>1</v>
       </c>
+      <c r="J52" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3423,16 +4237,16 @@
         </is>
       </c>
       <c r="C53" s="1" t="n">
-        <v>133849</v>
+        <v>365478</v>
       </c>
       <c r="D53" s="1" t="n">
-        <v>126297</v>
+        <v>343989</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>-7552</v>
+        <v>-21489</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>-0.05642178873207868</v>
+        <v>-0.05879697273160081</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -3440,16 +4254,19 @@
         </is>
       </c>
       <c r="H53" s="1" t="n">
-        <v>7552</v>
+        <v>21489</v>
       </c>
       <c r="I53" t="b">
+        <v>0</v>
+      </c>
+      <c r="J53" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3458,33 +4275,36 @@
         </is>
       </c>
       <c r="C54" s="1" t="n">
-        <v>246601</v>
+        <v>191888</v>
       </c>
       <c r="D54" s="1" t="n">
-        <v>264025</v>
+        <v>188125</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>17424</v>
+        <v>-3763</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>0.07065664778326122</v>
+        <v>-0.01961039773201034</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Unfavorable</t>
+          <t>Favorable</t>
         </is>
       </c>
       <c r="H54" s="1" t="n">
-        <v>17424</v>
+        <v>3763</v>
       </c>
       <c r="I54" t="b">
+        <v>0</v>
+      </c>
+      <c r="J54" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3493,33 +4313,36 @@
         </is>
       </c>
       <c r="C55" s="1" t="n">
-        <v>657601</v>
+        <v>4280</v>
       </c>
       <c r="D55" s="1" t="n">
-        <v>662257</v>
+        <v>4035</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>4656</v>
+        <v>-245</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>0.00708028120395194</v>
+        <v>-0.05724299065420561</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Unfavorable</t>
+          <t>Favorable</t>
         </is>
       </c>
       <c r="H55" s="1" t="n">
-        <v>4656</v>
+        <v>245</v>
       </c>
       <c r="I55" t="b">
+        <v>0</v>
+      </c>
+      <c r="J55" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3528,16 +4351,16 @@
         </is>
       </c>
       <c r="C56" s="1" t="n">
-        <v>121277</v>
+        <v>913634</v>
       </c>
       <c r="D56" s="1" t="n">
-        <v>127988</v>
+        <v>955629</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>6711</v>
+        <v>41995</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>0.05533613133570257</v>
+        <v>0.04596479553081431</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -3545,16 +4368,19 @@
         </is>
       </c>
       <c r="H56" s="1" t="n">
-        <v>6711</v>
+        <v>41995</v>
       </c>
       <c r="I56" t="b">
         <v>0</v>
+      </c>
+      <c r="J56" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3563,33 +4389,36 @@
         </is>
       </c>
       <c r="C57" s="1" t="n">
-        <v>37393</v>
+        <v>265515</v>
       </c>
       <c r="D57" s="1" t="n">
-        <v>40058</v>
+        <v>261937</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>2665</v>
+        <v>-3578</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>0.07127002380124622</v>
+        <v>-0.01347569817147807</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Unfavorable</t>
+          <t>Favorable</t>
         </is>
       </c>
       <c r="H57" s="1" t="n">
-        <v>2665</v>
+        <v>3578</v>
       </c>
       <c r="I57" t="b">
+        <v>0</v>
+      </c>
+      <c r="J57" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3598,16 +4427,16 @@
         </is>
       </c>
       <c r="C58" s="1" t="n">
-        <v>159710</v>
+        <v>156015</v>
       </c>
       <c r="D58" s="1" t="n">
-        <v>154478</v>
+        <v>147813</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>-5232</v>
+        <v>-8202</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>-0.03275937636967002</v>
+        <v>-0.05257186808960677</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -3615,16 +4444,19 @@
         </is>
       </c>
       <c r="H58" s="1" t="n">
-        <v>5232</v>
+        <v>8202</v>
       </c>
       <c r="I58" t="b">
+        <v>0</v>
+      </c>
+      <c r="J58" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3633,33 +4465,36 @@
         </is>
       </c>
       <c r="C59" s="1" t="n">
-        <v>82067</v>
+        <v>5158</v>
       </c>
       <c r="D59" s="1" t="n">
-        <v>76306</v>
+        <v>5220</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>-5761</v>
+        <v>62</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>-0.07019874005385843</v>
+        <v>0.01202016285381931</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Favorable</t>
+          <t>Unfavorable</t>
         </is>
       </c>
       <c r="H59" s="1" t="n">
-        <v>5761</v>
+        <v>62</v>
       </c>
       <c r="I59" t="b">
+        <v>0</v>
+      </c>
+      <c r="J59" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3668,16 +4503,16 @@
         </is>
       </c>
       <c r="C60" s="1" t="n">
-        <v>1239326</v>
+        <v>84135</v>
       </c>
       <c r="D60" s="1" t="n">
-        <v>1178634</v>
+        <v>77037</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>-60692</v>
+        <v>-7098</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>-0.04897177982225823</v>
+        <v>-0.08436441433410589</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -3685,16 +4520,19 @@
         </is>
       </c>
       <c r="H60" s="1" t="n">
-        <v>60692</v>
+        <v>7098</v>
       </c>
       <c r="I60" t="b">
+        <v>0</v>
+      </c>
+      <c r="J60" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3703,33 +4541,36 @@
         </is>
       </c>
       <c r="C61" s="1" t="n">
-        <v>770631</v>
+        <v>88385</v>
       </c>
       <c r="D61" s="1" t="n">
-        <v>760519</v>
+        <v>93830</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>-10112</v>
+        <v>5445</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>-0.01312171454301735</v>
+        <v>0.06160547604231487</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Favorable</t>
+          <t>Unfavorable</t>
         </is>
       </c>
       <c r="H61" s="1" t="n">
-        <v>10112</v>
+        <v>5445</v>
       </c>
       <c r="I61" t="b">
+        <v>0</v>
+      </c>
+      <c r="J61" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Customer Success</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3738,33 +4579,36 @@
         </is>
       </c>
       <c r="C62" s="1" t="n">
-        <v>1363</v>
+        <v>936211</v>
       </c>
       <c r="D62" s="1" t="n">
-        <v>1476</v>
+        <v>899294</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>113</v>
+        <v>-36917</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>0.08290535583272193</v>
+        <v>-0.03943235018601576</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Unfavorable</t>
+          <t>Favorable</t>
         </is>
       </c>
       <c r="H62" s="1" t="n">
-        <v>113</v>
+        <v>36917</v>
       </c>
       <c r="I62" t="b">
+        <v>0</v>
+      </c>
+      <c r="J62" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Customer Success</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3773,33 +4617,36 @@
         </is>
       </c>
       <c r="C63" s="1" t="n">
-        <v>139699</v>
+        <v>751664</v>
       </c>
       <c r="D63" s="1" t="n">
-        <v>133457</v>
+        <v>757440</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>-6242</v>
+        <v>5776</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>-0.04468178011295714</v>
+        <v>0.007684284467528044</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Favorable</t>
+          <t>Unfavorable</t>
         </is>
       </c>
       <c r="H63" s="1" t="n">
-        <v>6242</v>
+        <v>5776</v>
       </c>
       <c r="I63" t="b">
+        <v>0</v>
+      </c>
+      <c r="J63" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Customer Success</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3808,16 +4655,16 @@
         </is>
       </c>
       <c r="C64" s="1" t="n">
-        <v>105579</v>
+        <v>304068</v>
       </c>
       <c r="D64" s="1" t="n">
-        <v>105526</v>
+        <v>284414</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>-53</v>
+        <v>-19654</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>-0.0005019937677000161</v>
+        <v>-0.06463685754502282</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -3825,16 +4672,19 @@
         </is>
       </c>
       <c r="H64" s="1" t="n">
-        <v>53</v>
+        <v>19654</v>
       </c>
       <c r="I64" t="b">
+        <v>0</v>
+      </c>
+      <c r="J64" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Customer Success</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3843,33 +4693,36 @@
         </is>
       </c>
       <c r="C65" s="1" t="n">
-        <v>49083</v>
+        <v>850883</v>
       </c>
       <c r="D65" s="1" t="n">
-        <v>47323</v>
+        <v>897167</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>-1760</v>
+        <v>46284</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>-0.03585762891428804</v>
+        <v>0.05439525763236544</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Favorable</t>
+          <t>Unfavorable</t>
         </is>
       </c>
       <c r="H65" s="1" t="n">
-        <v>1760</v>
+        <v>46284</v>
       </c>
       <c r="I65" t="b">
+        <v>1</v>
+      </c>
+      <c r="J65" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Customer Success</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3878,16 +4731,16 @@
         </is>
       </c>
       <c r="C66" s="1" t="n">
-        <v>24951</v>
+        <v>30924</v>
       </c>
       <c r="D66" s="1" t="n">
-        <v>23984</v>
+        <v>28555</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>-967</v>
+        <v>-2369</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>-0.03875596168490241</v>
+        <v>-0.07660716595524512</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -3895,16 +4748,19 @@
         </is>
       </c>
       <c r="H66" s="1" t="n">
-        <v>967</v>
+        <v>2369</v>
       </c>
       <c r="I66" t="b">
+        <v>0</v>
+      </c>
+      <c r="J66" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Customer Success</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3913,33 +4769,36 @@
         </is>
       </c>
       <c r="C67" s="1" t="n">
-        <v>80494</v>
+        <v>72803</v>
       </c>
       <c r="D67" s="1" t="n">
-        <v>73783</v>
+        <v>79183</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>-6711</v>
+        <v>6380</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>-0.08337267373965761</v>
+        <v>0.08763375135640016</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Favorable</t>
+          <t>Unfavorable</t>
         </is>
       </c>
       <c r="H67" s="1" t="n">
-        <v>6711</v>
+        <v>6380</v>
       </c>
       <c r="I67" t="b">
+        <v>0</v>
+      </c>
+      <c r="J67" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Customer Success</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3948,16 +4807,16 @@
         </is>
       </c>
       <c r="C68" s="1" t="n">
-        <v>559505</v>
+        <v>15447</v>
       </c>
       <c r="D68" s="1" t="n">
-        <v>570539</v>
+        <v>16203</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>11034</v>
+        <v>756</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0.01972100338692237</v>
+        <v>0.04894154204699942</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -3965,16 +4824,19 @@
         </is>
       </c>
       <c r="H68" s="1" t="n">
-        <v>11034</v>
+        <v>756</v>
       </c>
       <c r="I68" t="b">
+        <v>0</v>
+      </c>
+      <c r="J68" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Customer Success</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3983,33 +4845,36 @@
         </is>
       </c>
       <c r="C69" s="1" t="n">
-        <v>76288</v>
+        <v>131343</v>
       </c>
       <c r="D69" s="1" t="n">
-        <v>76324</v>
+        <v>124220</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>36</v>
+        <v>-7123</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>0.0004718959731543624</v>
+        <v>-0.0542320489101056</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Unfavorable</t>
+          <t>Favorable</t>
         </is>
       </c>
       <c r="H69" s="1" t="n">
-        <v>36</v>
+        <v>7123</v>
       </c>
       <c r="I69" t="b">
+        <v>0</v>
+      </c>
+      <c r="J69" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Customer Success</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4018,16 +4883,16 @@
         </is>
       </c>
       <c r="C70" s="1" t="n">
-        <v>142939</v>
+        <v>164250</v>
       </c>
       <c r="D70" s="1" t="n">
-        <v>131398</v>
+        <v>149630</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>-11541</v>
+        <v>-14620</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>-0.08074073555852497</v>
+        <v>-0.08901065449010655</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -4035,16 +4900,19 @@
         </is>
       </c>
       <c r="H70" s="1" t="n">
-        <v>11541</v>
+        <v>14620</v>
       </c>
       <c r="I70" t="b">
+        <v>0</v>
+      </c>
+      <c r="J70" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Customer Success</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4053,33 +4921,36 @@
         </is>
       </c>
       <c r="C71" s="1" t="n">
-        <v>237254</v>
+        <v>105653</v>
       </c>
       <c r="D71" s="1" t="n">
-        <v>227800</v>
+        <v>111652</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>-9454</v>
+        <v>5999</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>-0.03984758950323282</v>
+        <v>0.05678021447568928</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Favorable</t>
+          <t>Unfavorable</t>
         </is>
       </c>
       <c r="H71" s="1" t="n">
-        <v>9454</v>
+        <v>5999</v>
       </c>
       <c r="I71" t="b">
+        <v>0</v>
+      </c>
+      <c r="J71" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Customer Success</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4088,16 +4959,16 @@
         </is>
       </c>
       <c r="C72" s="1" t="n">
-        <v>88324</v>
+        <v>588928</v>
       </c>
       <c r="D72" s="1" t="n">
-        <v>94814</v>
+        <v>610856</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>6490</v>
+        <v>21928</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>0.07347946198088855</v>
+        <v>0.03723375353184091</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -4105,16 +4976,19 @@
         </is>
       </c>
       <c r="H72" s="1" t="n">
-        <v>6490</v>
+        <v>21928</v>
       </c>
       <c r="I72" t="b">
+        <v>0</v>
+      </c>
+      <c r="J72" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Customer Success</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4123,33 +4997,36 @@
         </is>
       </c>
       <c r="C73" s="1" t="n">
-        <v>697211</v>
+        <v>147261</v>
       </c>
       <c r="D73" s="1" t="n">
-        <v>664526</v>
+        <v>153331</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>-32685</v>
+        <v>6070</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>-0.04687963901889098</v>
+        <v>0.04121933166282994</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Favorable</t>
+          <t>Unfavorable</t>
         </is>
       </c>
       <c r="H73" s="1" t="n">
-        <v>32685</v>
+        <v>6070</v>
       </c>
       <c r="I73" t="b">
+        <v>0</v>
+      </c>
+      <c r="J73" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>R&amp;D</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4158,33 +5035,36 @@
         </is>
       </c>
       <c r="C74" s="1" t="n">
-        <v>204546</v>
+        <v>32179</v>
       </c>
       <c r="D74" s="1" t="n">
-        <v>215530</v>
+        <v>32018</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>10984</v>
+        <v>-161</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>0.0536994123571226</v>
+        <v>-0.005003262997607135</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Unfavorable</t>
+          <t>Favorable</t>
         </is>
       </c>
       <c r="H74" s="1" t="n">
-        <v>10984</v>
+        <v>161</v>
       </c>
       <c r="I74" t="b">
+        <v>0</v>
+      </c>
+      <c r="J74" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>R&amp;D</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4193,16 +5073,16 @@
         </is>
       </c>
       <c r="C75" s="1" t="n">
-        <v>160450</v>
+        <v>185677</v>
       </c>
       <c r="D75" s="1" t="n">
-        <v>150362</v>
+        <v>172963</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>-10088</v>
+        <v>-12714</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>-0.0628731692115924</v>
+        <v>-0.06847374742159772</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -4210,16 +5090,19 @@
         </is>
       </c>
       <c r="H75" s="1" t="n">
-        <v>10088</v>
+        <v>12714</v>
       </c>
       <c r="I75" t="b">
+        <v>0</v>
+      </c>
+      <c r="J75" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>R&amp;D</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -4228,16 +5111,16 @@
         </is>
       </c>
       <c r="C76" s="1" t="n">
-        <v>217501</v>
+        <v>51513</v>
       </c>
       <c r="D76" s="1" t="n">
-        <v>217821</v>
+        <v>53490</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>320</v>
+        <v>1977</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>0.001471257603413318</v>
+        <v>0.03837866169704734</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -4245,16 +5128,19 @@
         </is>
       </c>
       <c r="H76" s="1" t="n">
-        <v>320</v>
+        <v>1977</v>
       </c>
       <c r="I76" t="b">
+        <v>0</v>
+      </c>
+      <c r="J76" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>R&amp;D</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -4263,16 +5149,16 @@
         </is>
       </c>
       <c r="C77" s="1" t="n">
-        <v>242694</v>
+        <v>831785</v>
       </c>
       <c r="D77" s="1" t="n">
-        <v>251248</v>
+        <v>870830</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>8554</v>
+        <v>39045</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>0.0352460299801396</v>
+        <v>0.04694121678077869</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -4280,16 +5166,19 @@
         </is>
       </c>
       <c r="H77" s="1" t="n">
-        <v>8554</v>
+        <v>39045</v>
       </c>
       <c r="I77" t="b">
         <v>0</v>
+      </c>
+      <c r="J77" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>R&amp;D</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -4298,16 +5187,16 @@
         </is>
       </c>
       <c r="C78" s="1" t="n">
-        <v>22781</v>
+        <v>408379</v>
       </c>
       <c r="D78" s="1" t="n">
-        <v>24250</v>
+        <v>412883</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>1469</v>
+        <v>4504</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>0.06448356086212194</v>
+        <v>0.01102897063756951</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -4315,16 +5204,19 @@
         </is>
       </c>
       <c r="H78" s="1" t="n">
-        <v>1469</v>
+        <v>4504</v>
       </c>
       <c r="I78" t="b">
+        <v>0</v>
+      </c>
+      <c r="J78" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>R&amp;D</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -4333,33 +5225,36 @@
         </is>
       </c>
       <c r="C79" s="1" t="n">
-        <v>124695</v>
+        <v>168077</v>
       </c>
       <c r="D79" s="1" t="n">
-        <v>120788</v>
+        <v>176274</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>-3907</v>
+        <v>8197</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>-0.03133245118088135</v>
+        <v>0.04876931406438716</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Favorable</t>
+          <t>Unfavorable</t>
         </is>
       </c>
       <c r="H79" s="1" t="n">
-        <v>3907</v>
+        <v>8197</v>
       </c>
       <c r="I79" t="b">
+        <v>0</v>
+      </c>
+      <c r="J79" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>R&amp;D</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -4368,16 +5263,16 @@
         </is>
       </c>
       <c r="C80" s="1" t="n">
-        <v>74922</v>
+        <v>27468</v>
       </c>
       <c r="D80" s="1" t="n">
-        <v>71149</v>
+        <v>27437</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>-3773</v>
+        <v>-31</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>-0.05035904006833774</v>
+        <v>-0.001128585990971312</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -4385,16 +5280,19 @@
         </is>
       </c>
       <c r="H80" s="1" t="n">
-        <v>3773</v>
+        <v>31</v>
       </c>
       <c r="I80" t="b">
+        <v>0</v>
+      </c>
+      <c r="J80" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>R&amp;D</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -4403,16 +5301,16 @@
         </is>
       </c>
       <c r="C81" s="1" t="n">
-        <v>439148</v>
+        <v>155809</v>
       </c>
       <c r="D81" s="1" t="n">
-        <v>455838</v>
+        <v>156446</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>16690</v>
+        <v>637</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>0.03800541047665024</v>
+        <v>0.004088338927789794</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -4420,16 +5318,19 @@
         </is>
       </c>
       <c r="H81" s="1" t="n">
-        <v>16690</v>
+        <v>637</v>
       </c>
       <c r="I81" t="b">
+        <v>0</v>
+      </c>
+      <c r="J81" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>R&amp;D</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -4438,33 +5339,36 @@
         </is>
       </c>
       <c r="C82" s="1" t="n">
-        <v>171698</v>
+        <v>164520</v>
       </c>
       <c r="D82" s="1" t="n">
-        <v>181263</v>
+        <v>162374</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>9565</v>
+        <v>-2146</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>0.05570827848897483</v>
+        <v>-0.01304400680768296</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Unfavorable</t>
+          <t>Favorable</t>
         </is>
       </c>
       <c r="H82" s="1" t="n">
-        <v>9565</v>
+        <v>2146</v>
       </c>
       <c r="I82" t="b">
+        <v>0</v>
+      </c>
+      <c r="J82" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>R&amp;D</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4473,16 +5377,16 @@
         </is>
       </c>
       <c r="C83" s="1" t="n">
-        <v>1107759</v>
+        <v>547074</v>
       </c>
       <c r="D83" s="1" t="n">
-        <v>1077583</v>
+        <v>500340</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>-30176</v>
+        <v>-46734</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>-0.02724058211217422</v>
+        <v>-0.08542537207032321</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -4490,16 +5394,19 @@
         </is>
       </c>
       <c r="H83" s="1" t="n">
-        <v>30176</v>
+        <v>46734</v>
       </c>
       <c r="I83" t="b">
+        <v>1</v>
+      </c>
+      <c r="J83" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>R&amp;D</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4508,16 +5415,16 @@
         </is>
       </c>
       <c r="C84" s="1" t="n">
-        <v>137497</v>
+        <v>424520</v>
       </c>
       <c r="D84" s="1" t="n">
-        <v>127502</v>
+        <v>394557</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>-9995</v>
+        <v>-29963</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>-0.07269249510898419</v>
+        <v>-0.07058089135965326</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -4525,16 +5432,19 @@
         </is>
       </c>
       <c r="H84" s="1" t="n">
-        <v>9995</v>
+        <v>29963</v>
       </c>
       <c r="I84" t="b">
+        <v>1</v>
+      </c>
+      <c r="J84" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>R&amp;D</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4543,33 +5453,36 @@
         </is>
       </c>
       <c r="C85" s="1" t="n">
-        <v>458038</v>
+        <v>912818</v>
       </c>
       <c r="D85" s="1" t="n">
-        <v>494357</v>
+        <v>835828</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>36319</v>
+        <v>-76990</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>0.07929254777987853</v>
+        <v>-0.08434320970883571</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Unfavorable</t>
+          <t>Favorable</t>
         </is>
       </c>
       <c r="H85" s="1" t="n">
-        <v>36319</v>
+        <v>76990</v>
       </c>
       <c r="I85" t="b">
         <v>1</v>
       </c>
+      <c r="J85" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4578,33 +5491,36 @@
         </is>
       </c>
       <c r="C86" s="1" t="n">
-        <v>107335</v>
+        <v>284101</v>
       </c>
       <c r="D86" s="1" t="n">
-        <v>116922</v>
+        <v>267910</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>9587</v>
+        <v>-16191</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>0.08931848884334094</v>
+        <v>-0.05699029570469657</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Unfavorable</t>
+          <t>Favorable</t>
         </is>
       </c>
       <c r="H86" s="1" t="n">
-        <v>9587</v>
+        <v>16191</v>
       </c>
       <c r="I86" t="b">
+        <v>0</v>
+      </c>
+      <c r="J86" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4613,33 +5529,36 @@
         </is>
       </c>
       <c r="C87" s="1" t="n">
-        <v>267622</v>
+        <v>52786</v>
       </c>
       <c r="D87" s="1" t="n">
-        <v>290042</v>
+        <v>50926</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>22420</v>
+        <v>-1860</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>0.08377487650492112</v>
+        <v>-0.03523661576933278</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Unfavorable</t>
+          <t>Favorable</t>
         </is>
       </c>
       <c r="H87" s="1" t="n">
-        <v>22420</v>
+        <v>1860</v>
       </c>
       <c r="I87" t="b">
+        <v>0</v>
+      </c>
+      <c r="J87" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4648,16 +5567,16 @@
         </is>
       </c>
       <c r="C88" s="1" t="n">
-        <v>165729</v>
+        <v>52777</v>
       </c>
       <c r="D88" s="1" t="n">
-        <v>167467</v>
+        <v>53012</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>1738</v>
+        <v>235</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>0.01048699986121922</v>
+        <v>0.004452697197642913</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -4665,16 +5584,19 @@
         </is>
       </c>
       <c r="H88" s="1" t="n">
-        <v>1738</v>
+        <v>235</v>
       </c>
       <c r="I88" t="b">
+        <v>0</v>
+      </c>
+      <c r="J88" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4683,33 +5605,36 @@
         </is>
       </c>
       <c r="C89" s="1" t="n">
-        <v>195575</v>
+        <v>18621</v>
       </c>
       <c r="D89" s="1" t="n">
-        <v>209045</v>
+        <v>18392</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>13470</v>
+        <v>-229</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>0.06887383356768503</v>
+        <v>-0.01229794318242844</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Unfavorable</t>
+          <t>Favorable</t>
         </is>
       </c>
       <c r="H89" s="1" t="n">
-        <v>13470</v>
+        <v>229</v>
       </c>
       <c r="I89" t="b">
+        <v>0</v>
+      </c>
+      <c r="J89" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4718,16 +5643,16 @@
         </is>
       </c>
       <c r="C90" s="1" t="n">
-        <v>34520</v>
+        <v>625881</v>
       </c>
       <c r="D90" s="1" t="n">
-        <v>32585</v>
+        <v>602361</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>-1935</v>
+        <v>-23520</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>-0.05605446118192352</v>
+        <v>-0.03757902860128363</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -4735,16 +5660,19 @@
         </is>
       </c>
       <c r="H90" s="1" t="n">
-        <v>1935</v>
+        <v>23520</v>
       </c>
       <c r="I90" t="b">
+        <v>0</v>
+      </c>
+      <c r="J90" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4753,33 +5681,36 @@
         </is>
       </c>
       <c r="C91" s="1" t="n">
-        <v>114751</v>
+        <v>286012</v>
       </c>
       <c r="D91" s="1" t="n">
-        <v>110183</v>
+        <v>291770</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>-4568</v>
+        <v>5758</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>-0.03980793195701998</v>
+        <v>0.02013202243262521</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Favorable</t>
+          <t>Unfavorable</t>
         </is>
       </c>
       <c r="H91" s="1" t="n">
-        <v>4568</v>
+        <v>5758</v>
       </c>
       <c r="I91" t="b">
+        <v>0</v>
+      </c>
+      <c r="J91" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4788,33 +5719,36 @@
         </is>
       </c>
       <c r="C92" s="1" t="n">
-        <v>175143</v>
+        <v>383156</v>
       </c>
       <c r="D92" s="1" t="n">
-        <v>181459</v>
+        <v>358292</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>6316</v>
+        <v>-24864</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0.03606196079774813</v>
+        <v>-0.06489262858992161</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Unfavorable</t>
+          <t>Favorable</t>
         </is>
       </c>
       <c r="H92" s="1" t="n">
-        <v>6316</v>
+        <v>24864</v>
       </c>
       <c r="I92" t="b">
+        <v>0</v>
+      </c>
+      <c r="J92" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4823,33 +5757,36 @@
         </is>
       </c>
       <c r="C93" s="1" t="n">
-        <v>38190</v>
+        <v>6473</v>
       </c>
       <c r="D93" s="1" t="n">
-        <v>40573</v>
+        <v>6230</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>2383</v>
+        <v>-243</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>0.06239853364755171</v>
+        <v>-0.03754055306658427</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Unfavorable</t>
+          <t>Favorable</t>
         </is>
       </c>
       <c r="H93" s="1" t="n">
-        <v>2383</v>
+        <v>243</v>
       </c>
       <c r="I93" t="b">
+        <v>0</v>
+      </c>
+      <c r="J93" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4858,33 +5795,36 @@
         </is>
       </c>
       <c r="C94" s="1" t="n">
-        <v>28305</v>
+        <v>1090283</v>
       </c>
       <c r="D94" s="1" t="n">
-        <v>30120</v>
+        <v>1064056</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>1815</v>
+        <v>-26227</v>
       </c>
       <c r="F94" s="3" t="n">
-        <v>0.06412294647588765</v>
+        <v>-0.02405522235969927</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Unfavorable</t>
+          <t>Favorable</t>
         </is>
       </c>
       <c r="H94" s="1" t="n">
-        <v>1815</v>
+        <v>26227</v>
       </c>
       <c r="I94" t="b">
+        <v>0</v>
+      </c>
+      <c r="J94" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4893,16 +5833,16 @@
         </is>
       </c>
       <c r="C95" s="1" t="n">
-        <v>592649</v>
+        <v>555924</v>
       </c>
       <c r="D95" s="1" t="n">
-        <v>582462</v>
+        <v>551528</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>-10187</v>
+        <v>-4396</v>
       </c>
       <c r="F95" s="3" t="n">
-        <v>-0.01718892632907505</v>
+        <v>-0.007907555709053755</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -4910,16 +5850,19 @@
         </is>
       </c>
       <c r="H95" s="1" t="n">
-        <v>10187</v>
+        <v>4396</v>
       </c>
       <c r="I95" t="b">
+        <v>0</v>
+      </c>
+      <c r="J95" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4928,16 +5871,16 @@
         </is>
       </c>
       <c r="C96" s="1" t="n">
-        <v>106995</v>
+        <v>74278</v>
       </c>
       <c r="D96" s="1" t="n">
-        <v>114463</v>
+        <v>78090</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>7468</v>
+        <v>3812</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>0.06979765409598579</v>
+        <v>0.05132071407415385</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -4945,16 +5888,19 @@
         </is>
       </c>
       <c r="H96" s="1" t="n">
-        <v>7468</v>
+        <v>3812</v>
       </c>
       <c r="I96" t="b">
+        <v>0</v>
+      </c>
+      <c r="J96" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4963,26 +5909,29 @@
         </is>
       </c>
       <c r="C97" s="1" t="n">
-        <v>44481</v>
+        <v>62450</v>
       </c>
       <c r="D97" s="1" t="n">
-        <v>47290</v>
+        <v>59074</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>2809</v>
+        <v>-3376</v>
       </c>
       <c r="F97" s="3" t="n">
-        <v>0.06315055866549762</v>
+        <v>-0.05405924739791833</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Unfavorable</t>
+          <t>Favorable</t>
         </is>
       </c>
       <c r="H97" s="1" t="n">
-        <v>2809</v>
+        <v>3376</v>
       </c>
       <c r="I97" t="b">
+        <v>0</v>
+      </c>
+      <c r="J97" t="b">
         <v>0</v>
       </c>
     </row>
